--- a/Milk_stage_data.xlsx
+++ b/Milk_stage_data.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajen\OneDrive\Desktop\Arranged_Dataset\Li_6800\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmishra\OneDrive - Kansas State University\Desktop\Draft Manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E88495-F58A-445F-A44C-030A19A8864D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE53F27F-4053-43D5-A013-15DE63561ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="7-25-Plt7-P11" sheetId="2" r:id="rId1"/>
-    <sheet name="7-25-Plt16-P08" sheetId="3" r:id="rId2"/>
-    <sheet name="7-25_plt19_H3" sheetId="6" r:id="rId3"/>
-    <sheet name="7-27-Plt1-P10" sheetId="5" r:id="rId4"/>
-    <sheet name="7-28_Plt23_7" sheetId="7" r:id="rId5"/>
-    <sheet name="7-28_Plt27_P2" sheetId="8" r:id="rId6"/>
+    <sheet name="7-25-Plt7-R1-M2-H1-P11" sheetId="2" r:id="rId1"/>
+    <sheet name=" 7-25-Plt16-R2-M1-H2-P08" sheetId="3" r:id="rId2"/>
+    <sheet name=" 7-25_plt19-R3-M1-H1-P2" sheetId="6" r:id="rId3"/>
+    <sheet name="7-27-Plt1-R1-M2-H1-P10" sheetId="5" r:id="rId4"/>
+    <sheet name="7-28_Plt23-R3-M3-H2-P7" sheetId="7" r:id="rId5"/>
+    <sheet name="7-28_Plt27-R3-M3-H1-P2" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2585,9 +2585,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ABF67BF-7B42-4871-B8A8-99A8BDB7F28C}">
   <dimension ref="A2:KJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>96.9</v>
       </c>
     </row>
-    <row r="6" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>0</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>0.2175</v>
       </c>
     </row>
-    <row r="10" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>-6276</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>368</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>97.3245</v>
       </c>
     </row>
-    <row r="18" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>97.313599999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -7786,7 +7786,7 @@
         <v>97.300299999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>97.289599999999993</v>
       </c>
     </row>
-    <row r="21" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>5</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>97.282200000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>6</v>
       </c>
@@ -10291,7 +10291,7 @@
         <v>97.285300000000007</v>
       </c>
     </row>
-    <row r="23" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -11126,7 +11126,7 @@
         <v>97.2804</v>
       </c>
     </row>
-    <row r="24" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>8</v>
       </c>
@@ -11961,7 +11961,7 @@
         <v>97.267700000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>97.255300000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>10</v>
       </c>
@@ -13631,7 +13631,7 @@
         <v>97.245000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11</v>
       </c>
@@ -14466,7 +14466,7 @@
         <v>97.2303</v>
       </c>
     </row>
-    <row r="28" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>97.229500000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13</v>
       </c>
@@ -16144,9 +16144,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE46CE57-92D9-4E3C-82CA-40D49E135E51}">
   <dimension ref="A2:KJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -16157,7 +16157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -16165,7 +16165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -16200,7 +16200,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -16232,7 +16232,7 @@
         <v>96.9</v>
       </c>
     </row>
-    <row r="6" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -16249,7 +16249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>0</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -16316,7 +16316,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -16366,7 +16366,7 @@
         <v>0.2175</v>
       </c>
     </row>
-    <row r="10" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -16386,7 +16386,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>0</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -16429,7 +16429,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>-6276</v>
       </c>
@@ -16452,7 +16452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -17342,7 +17342,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -18232,7 +18232,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>368</v>
       </c>
@@ -18840,7 +18840,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -19675,7 +19675,7 @@
         <v>97.051599999999993</v>
       </c>
     </row>
-    <row r="18" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -20510,7 +20510,7 @@
         <v>97.031999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -21345,7 +21345,7 @@
         <v>97.031999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -22180,7 +22180,7 @@
         <v>97.034199999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>5</v>
       </c>
@@ -23015,7 +23015,7 @@
         <v>97.036500000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>6</v>
       </c>
@@ -23850,7 +23850,7 @@
         <v>97.036699999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -24685,7 +24685,7 @@
         <v>97.043800000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>8</v>
       </c>
@@ -25520,7 +25520,7 @@
         <v>97.037099999999995</v>
       </c>
     </row>
-    <row r="25" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9</v>
       </c>
@@ -26355,7 +26355,7 @@
         <v>97.027799999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>10</v>
       </c>
@@ -27190,7 +27190,7 @@
         <v>97.030299999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11</v>
       </c>
@@ -28025,7 +28025,7 @@
         <v>97.048100000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12</v>
       </c>
@@ -28860,7 +28860,7 @@
         <v>97.041399999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13</v>
       </c>
@@ -29703,9 +29703,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0BB631F-261D-4B64-93BD-90C5C6C568F9}">
   <dimension ref="A2:KJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -29716,7 +29716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -29724,7 +29724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -29759,7 +29759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -29791,7 +29791,7 @@
         <v>96.9</v>
       </c>
     </row>
-    <row r="6" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -29808,7 +29808,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>0</v>
       </c>
@@ -29822,7 +29822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -29875,7 +29875,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -29925,7 +29925,7 @@
         <v>0.2175</v>
       </c>
     </row>
-    <row r="10" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -29945,7 +29945,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>0</v>
       </c>
@@ -29962,7 +29962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -29988,7 +29988,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>-6276</v>
       </c>
@@ -30011,7 +30011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -30901,7 +30901,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -31791,7 +31791,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>368</v>
       </c>
@@ -32399,7 +32399,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -33234,7 +33234,7 @@
         <v>96.549800000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -34069,7 +34069,7 @@
         <v>96.483999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -34904,7 +34904,7 @@
         <v>96.4529</v>
       </c>
     </row>
-    <row r="20" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -35739,7 +35739,7 @@
         <v>96.410899999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>5</v>
       </c>
@@ -36574,7 +36574,7 @@
         <v>96.380700000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>6</v>
       </c>
@@ -37409,7 +37409,7 @@
         <v>96.360600000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -38244,7 +38244,7 @@
         <v>96.345100000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>8</v>
       </c>
@@ -39079,7 +39079,7 @@
         <v>96.316900000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9</v>
       </c>
@@ -39914,7 +39914,7 @@
         <v>96.309700000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>10</v>
       </c>
@@ -40749,7 +40749,7 @@
         <v>96.310100000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11</v>
       </c>
@@ -41584,7 +41584,7 @@
         <v>96.304199999999994</v>
       </c>
     </row>
-    <row r="28" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12</v>
       </c>
@@ -42419,7 +42419,7 @@
         <v>96.289199999999994</v>
       </c>
     </row>
-    <row r="29" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13</v>
       </c>
@@ -43262,9 +43262,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322BE17A-836D-41CB-BA00-93EFEFB36611}">
   <dimension ref="A2:KJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -43275,7 +43275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -43283,7 +43283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -43318,7 +43318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -43350,7 +43350,7 @@
         <v>96.9</v>
       </c>
     </row>
-    <row r="6" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -43367,7 +43367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>0</v>
       </c>
@@ -43381,7 +43381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -43434,7 +43434,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -43484,7 +43484,7 @@
         <v>0.2175</v>
       </c>
     </row>
-    <row r="10" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -43504,7 +43504,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>0</v>
       </c>
@@ -43521,7 +43521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -43547,7 +43547,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>-6276</v>
       </c>
@@ -43570,7 +43570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -44460,7 +44460,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -45350,7 +45350,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>368</v>
       </c>
@@ -45958,7 +45958,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -46793,7 +46793,7 @@
         <v>97.037499999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -47628,7 +47628,7 @@
         <v>97.031400000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -48463,7 +48463,7 @@
         <v>97.026399999999995</v>
       </c>
     </row>
-    <row r="20" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -49298,7 +49298,7 @@
         <v>97.008099999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>5</v>
       </c>
@@ -50133,7 +50133,7 @@
         <v>97.001099999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>6</v>
       </c>
@@ -50968,7 +50968,7 @@
         <v>96.981300000000005</v>
       </c>
     </row>
-    <row r="23" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -51803,7 +51803,7 @@
         <v>96.969200000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>8</v>
       </c>
@@ -52638,7 +52638,7 @@
         <v>96.955399999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9</v>
       </c>
@@ -53473,7 +53473,7 @@
         <v>96.950999999999993</v>
       </c>
     </row>
-    <row r="26" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>10</v>
       </c>
@@ -54308,7 +54308,7 @@
         <v>96.930499999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11</v>
       </c>
@@ -55143,7 +55143,7 @@
         <v>96.933499999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12</v>
       </c>
@@ -55978,7 +55978,7 @@
         <v>96.923699999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13</v>
       </c>
@@ -56821,9 +56821,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63508E7E-C07D-4395-9661-3C7C0217D4C9}">
   <dimension ref="A2:KJ29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -56834,7 +56834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -56842,7 +56842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -56877,7 +56877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -56909,7 +56909,7 @@
         <v>96.9</v>
       </c>
     </row>
-    <row r="6" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -56926,7 +56926,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>0</v>
       </c>
@@ -56940,7 +56940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -56993,7 +56993,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -57043,7 +57043,7 @@
         <v>0.2175</v>
       </c>
     </row>
-    <row r="10" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -57063,7 +57063,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>0</v>
       </c>
@@ -57080,7 +57080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -57106,7 +57106,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>-6276</v>
       </c>
@@ -57129,7 +57129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -58019,7 +58019,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -58909,7 +58909,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>368</v>
       </c>
@@ -59517,7 +59517,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -60352,7 +60352,7 @@
         <v>97.4208</v>
       </c>
     </row>
-    <row r="18" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -61187,7 +61187,7 @@
         <v>97.427199999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -62022,7 +62022,7 @@
         <v>97.431399999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -62857,7 +62857,7 @@
         <v>97.430300000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>5</v>
       </c>
@@ -63692,7 +63692,7 @@
         <v>97.431799999999996</v>
       </c>
     </row>
-    <row r="22" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>6</v>
       </c>
@@ -64527,7 +64527,7 @@
         <v>97.424499999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -65362,7 +65362,7 @@
         <v>97.418199999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>8</v>
       </c>
@@ -66197,7 +66197,7 @@
         <v>97.412700000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9</v>
       </c>
@@ -67032,7 +67032,7 @@
         <v>97.4084</v>
       </c>
     </row>
-    <row r="26" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>10</v>
       </c>
@@ -67867,7 +67867,7 @@
         <v>97.401499999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11</v>
       </c>
@@ -68702,7 +68702,7 @@
         <v>97.387500000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12</v>
       </c>
@@ -69537,7 +69537,7 @@
         <v>97.371300000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13</v>
       </c>
@@ -70380,9 +70380,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6582D938-5A6F-4281-9DD0-C65B12D33826}">
   <dimension ref="A2:KJ32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -70393,7 +70393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -70401,7 +70401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -70436,7 +70436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>16</v>
       </c>
@@ -70468,7 +70468,7 @@
         <v>96.9</v>
       </c>
     </row>
-    <row r="6" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -70485,7 +70485,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>0</v>
       </c>
@@ -70499,7 +70499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -70552,7 +70552,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>40</v>
       </c>
@@ -70602,7 +70602,7 @@
         <v>0.2175</v>
       </c>
     </row>
-    <row r="10" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -70622,7 +70622,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>0</v>
       </c>
@@ -70639,7 +70639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -70665,7 +70665,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>-6276</v>
       </c>
@@ -70688,7 +70688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -71578,7 +71578,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>78</v>
       </c>
@@ -72468,7 +72468,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:296" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>368</v>
       </c>
@@ -73076,7 +73076,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="17" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1</v>
       </c>
@@ -73911,7 +73911,7 @@
         <v>97.538700000000006</v>
       </c>
     </row>
-    <row r="18" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -74746,7 +74746,7 @@
         <v>97.543999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3</v>
       </c>
@@ -75581,7 +75581,7 @@
         <v>97.551599999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4</v>
       </c>
@@ -76416,7 +76416,7 @@
         <v>97.558400000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>5</v>
       </c>
@@ -77251,7 +77251,7 @@
         <v>97.564700000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>6</v>
       </c>
@@ -78086,7 +78086,7 @@
         <v>97.555300000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>7</v>
       </c>
@@ -78921,7 +78921,7 @@
         <v>97.564300000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>8</v>
       </c>
@@ -79756,7 +79756,7 @@
         <v>97.5565</v>
       </c>
     </row>
-    <row r="25" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9</v>
       </c>
@@ -80591,7 +80591,7 @@
         <v>97.554400000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>10</v>
       </c>
@@ -81426,7 +81426,7 @@
         <v>97.554699999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>11</v>
       </c>
@@ -82261,7 +82261,7 @@
         <v>97.546700000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12</v>
       </c>
@@ -83096,7 +83096,7 @@
         <v>97.537400000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>13</v>
       </c>
@@ -83931,7 +83931,7 @@
         <v>97.520300000000006</v>
       </c>
     </row>
-    <row r="30" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>14</v>
       </c>
@@ -84766,7 +84766,7 @@
         <v>97.49</v>
       </c>
     </row>
-    <row r="31" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>15</v>
       </c>
@@ -85601,7 +85601,7 @@
         <v>97.464699999999993</v>
       </c>
     </row>
-    <row r="32" spans="1:296" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:296" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>16</v>
       </c>
